--- a/artfynd/A 20242-2025 artfynd.xlsx
+++ b/artfynd/A 20242-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -788,6 +788,205 @@
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
       </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>126348509</v>
+      </c>
+      <c r="B3" t="n">
+        <v>98266</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>219790</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Digerberget, Hjd</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>411787</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6966228</v>
+      </c>
+      <c r="S3" t="n">
+        <v>10</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2025-06-30</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2025-06-30</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>126348495</v>
+      </c>
+      <c r="B4" t="n">
+        <v>57656</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Digerberget, Hjd</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>411796</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6966208</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2025-06-30</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2025-06-30</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Ringhack färska</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 20242-2025 artfynd.xlsx
+++ b/artfynd/A 20242-2025 artfynd.xlsx
@@ -794,7 +794,7 @@
         <v>126348509</v>
       </c>
       <c r="B3" t="n">
-        <v>98266</v>
+        <v>98269</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 20242-2025 artfynd.xlsx
+++ b/artfynd/A 20242-2025 artfynd.xlsx
@@ -794,7 +794,7 @@
         <v>126348509</v>
       </c>
       <c r="B3" t="n">
-        <v>98269</v>
+        <v>98278</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -891,7 +891,7 @@
         <v>126348495</v>
       </c>
       <c r="B4" t="n">
-        <v>57656</v>
+        <v>57657</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 20242-2025 artfynd.xlsx
+++ b/artfynd/A 20242-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,12 +678,7 @@
         <v>91992995</v>
       </c>
       <c r="B2" t="n">
-        <v>77258</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79084</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>411882.1565591205</v>
+        <v>411882</v>
       </c>
       <c r="R2" t="n">
-        <v>6966329.069379739</v>
+        <v>6966329</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -748,19 +743,9 @@
           <t>2018-06-01</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2018-10-31</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -791,32 +776,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>126348509</v>
+        <v>126348495</v>
       </c>
       <c r="B3" t="n">
-        <v>98278</v>
+        <v>57953</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>219790</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -826,10 +811,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>411787</v>
+        <v>411796</v>
       </c>
       <c r="R3" t="n">
-        <v>6966228</v>
+        <v>6966208</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -862,6 +847,11 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-06-30</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -888,32 +878,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>126348495</v>
+        <v>126348509</v>
       </c>
       <c r="B4" t="n">
-        <v>57657</v>
+        <v>99035</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>219790</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -923,10 +913,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>411796</v>
+        <v>411787</v>
       </c>
       <c r="R4" t="n">
-        <v>6966208</v>
+        <v>6966228</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -961,11 +951,6 @@
           <t>2025-06-30</t>
         </is>
       </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Ringhack färska</t>
-        </is>
-      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
@@ -987,6 +972,103 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>126348508</v>
+      </c>
+      <c r="B5" t="n">
+        <v>97989</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>221941</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Plattlummer</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Lycopodium complanatum</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Digerberget, Hjd</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>411930</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6966300</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025-06-30</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2025-06-30</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 20242-2025 artfynd.xlsx
+++ b/artfynd/A 20242-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AZ5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -773,6 +778,11 @@
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/91992995</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -875,6 +885,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126348495</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -972,6 +987,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126348509</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1069,8 +1089,19 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126348508</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>